--- a/output.xlsx
+++ b/output.xlsx
@@ -36,26 +36,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Canadian-United States-Mexico Agreement (CUSMA)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF076DD3"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Trada Mexico Estados Unido Canada (T-MEC)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF076DD3"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+Canadian-United States-Mexico Agreement (CUSMA)
+Trada Mexico Estados Unido Canada (T-MEC)
 Unites States-Mexico-Canada Agreement (USMCA)</t>
     </r>
   </si>

--- a/output.xlsx
+++ b/output.xlsx
@@ -1,63 +1,225 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="My Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="My Sheet" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <r>
       <rPr>
         <b/>
+        <color rgb="#005cc5"/>
         <sz val="36"/>
-        <color rgb="FF076DD3"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Certification of Origin</t>
+      <t>Certification of Origin</t>
     </r>
     <r>
       <rPr>
+        <color rgb="#005cc5"/>
         <sz val="18"/>
-        <color rgb="FF076DD3"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Canadian-United States-Mexico Agreement (CUSMA)
-Trada Mexico Estados Unido Canada (T-MEC)
+Canadian-United States-Mexico Agreement (CUSMA)</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="#005cc5"/>
+        <sz val="18"/>
+      </rPr>
+      <t xml:space="preserve">
+Trada Mexico Estados Unido Canada (T-MEC)</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="#005cc5"/>
+        <sz val="18"/>
+      </rPr>
+      <t xml:space="preserve">
 Unites States-Mexico-Canada Agreement (USMCA)</t>
     </r>
+  </si>
+  <si>
+    <t>1. Blanket Period: (dd/mm/yyyy)</t>
+  </si>
+  <si>
+    <t>From:</t>
+  </si>
+  <si>
+    <t>To:</t>
+  </si>
+  <si>
+    <t>3. Certifier's Name and Address:</t>
+  </si>
+  <si>
+    <t>4. Exporter's Name and Address:</t>
+  </si>
+  <si>
+    <t>HI-TECH SEALS INC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS PER CERTIFIER </t>
+  </si>
+  <si>
+    <t>9211 - 41 AVENUE NW</t>
+  </si>
+  <si>
+    <t>EDMONTON,, AB</t>
+  </si>
+  <si>
+    <t>T6E 6R5</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Telephone:</t>
+  </si>
+  <si>
+    <t>780.438.6055   TAX IDENTIFICATION #: 122781925RM0001</t>
+  </si>
+  <si>
+    <t>E-Mail Address:</t>
+  </si>
+  <si>
+    <t>alina.hladkina@hitechseals.com</t>
+  </si>
+  <si>
+    <t>Certifying Party:</t>
+  </si>
+  <si>
+    <t>5. Producer's Name and Address:</t>
+  </si>
+  <si>
+    <t>6. Importer's Name and Address:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS PER THE CERTIFIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUSTOMER'S ADDRESS </t>
+  </si>
+  <si>
+    <t>HI-TECH SEALS - BROUSSARD</t>
+  </si>
+  <si>
+    <t>909 GARBER RD</t>
+  </si>
+  <si>
+    <t>BROUSSARD,, LA 70518</t>
+  </si>
+  <si>
+    <t>7a. Part Number</t>
+  </si>
+  <si>
+    <t>7b. Description of the Goods</t>
+  </si>
+  <si>
+    <t>8. HS Tariff Classification</t>
+  </si>
+  <si>
+    <t>9. Origin Criterion</t>
+  </si>
+  <si>
+    <t>10. Country of Origin</t>
+  </si>
+  <si>
+    <t>INV# 1408731</t>
+  </si>
+  <si>
+    <t>PO# 4472-BRO</t>
+  </si>
+  <si>
+    <t>HES 6010512516AR</t>
+  </si>
+  <si>
+    <t>PLASTIC SEAL ASSORT SET</t>
+  </si>
+  <si>
+    <t>3926.90.45.90</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>INV# 1408842</t>
+  </si>
+  <si>
+    <t>PO# 4464-BRO</t>
+  </si>
+  <si>
+    <t>FET M406E150</t>
+  </si>
+  <si>
+    <t>PLASTIC SEAL</t>
+  </si>
+  <si>
+    <t>INV# 1409009</t>
+  </si>
+  <si>
+    <t>PO# 4538-BRO</t>
+  </si>
+  <si>
+    <t>HES 3080000045</t>
+  </si>
+  <si>
+    <t>PLASTIC BACK UP RING</t>
+  </si>
+  <si>
+    <t>HTL 12500375</t>
+  </si>
+  <si>
+    <t>PLASTIC U CUP</t>
+  </si>
+  <si>
+    <t>US</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
-      <color rgb="FF076DD3"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,25 +230,145 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="3" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="3" vertical="center" wrapText="1"/>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -105,7 +387,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -151,13 +433,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -180,18 +462,19 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -214,6 +497,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -248,20 +532,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -383,215 +663,9 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -610,7 +684,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr bwMode="auto"/>
+      <a:spPr/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -629,38 +703,601 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N47"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="14" width="9.8" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="195.94999999999999" customHeight="1">
+    <row r="1" ht="195.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6">
+        <v>45826.18428253473</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46190.18428253473</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" ht="20.1" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" ht="39.95" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="17"/>
+      <c r="J21" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="16"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="21"/>
+      <c r="L23" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M23" s="21"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="21"/>
+      <c r="L26" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" s="21"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" s="21"/>
+      <c r="L29" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M29" s="21"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="2:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="21"/>
+      <c r="L30" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" s="21"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="57.95" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20.1" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20.1" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20.1" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20.1" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20.1" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20.1" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="67">
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:M3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="H6:M10"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="B15:G18"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M20"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="L30:M30"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>